--- a/myPortfolioManagement/MeteoraGlobalEquityFund/Data/similar_companies.xlsx
+++ b/myPortfolioManagement/MeteoraGlobalEquityFund/Data/similar_companies.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="16"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="ALB" sheetId="1" state="visible" r:id="rId1"/>
@@ -2618,7 +2618,6 @@
       <c r="N9">
         <v>25860000000</v>
       </c>
-      <c r="O9"/>
       <c r="P9">
         <v>30.010000000000002</v>
       </c>
@@ -2736,7 +2735,6 @@
       <c r="N11">
         <v>19960000000</v>
       </c>
-      <c r="O11"/>
       <c r="P11">
         <v>78.260000000000005</v>
       </c>
@@ -2807,7 +2805,7 @@
         <v>357814</v>
       </c>
       <c r="S12">
-        <f>N10/1000000000</f>
+        <f t="shared" ref="S12:S13" si="0">N10/1000000000</f>
         <v>24.050000000000001</v>
       </c>
     </row>
@@ -2867,7 +2865,7 @@
         <v>306705</v>
       </c>
       <c r="S13">
-        <f>N11/1000000000</f>
+        <f t="shared" si="0"/>
         <v>19.960000000000001</v>
       </c>
     </row>
@@ -3154,7 +3152,6 @@
       <c r="N18">
         <v>7700000000</v>
       </c>
-      <c r="O18"/>
       <c r="P18">
         <v>33.939999999999998</v>
       </c>
@@ -3225,7 +3222,7 @@
         <v>1561392</v>
       </c>
       <c r="S19">
-        <f>N20/1000000000</f>
+        <f t="shared" ref="S19:S20" si="1">N20/1000000000</f>
         <v>4.5800000000000001</v>
       </c>
     </row>
@@ -3285,7 +3282,7 @@
         <v>1616099</v>
       </c>
       <c r="S20">
-        <f>N21/1000000000</f>
+        <f t="shared" si="1"/>
         <v>3.5499999999999998</v>
       </c>
     </row>
@@ -3422,7 +3419,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="10" max="10" width="28.7109375"/>
     <col bestFit="1" min="11" max="11" width="13.57421875"/>
@@ -3584,7 +3581,6 @@
       <c r="N3">
         <v>120.84</v>
       </c>
-      <c r="O3"/>
       <c r="P3">
         <v>203.63</v>
       </c>
@@ -3638,7 +3634,6 @@
       <c r="N4">
         <v>700.59000000000003</v>
       </c>
-      <c r="O4"/>
       <c r="P4">
         <v>320.60000000000002</v>
       </c>
@@ -3916,7 +3911,6 @@
       <c r="N9">
         <v>7.7000000000000002</v>
       </c>
-      <c r="O9"/>
       <c r="P9">
         <v>33.939999999999998</v>
       </c>
@@ -4049,7 +4043,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="10" max="10" width="20.07421875"/>
     <col bestFit="1" min="11" max="11" width="18.2109375"/>
@@ -4266,7 +4260,6 @@
       <c r="N4">
         <v>10.640000000000001</v>
       </c>
-      <c r="O4"/>
       <c r="P4">
         <v>85.530000000000001</v>
       </c>
@@ -4623,7 +4616,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="10" max="10" width="38.140625"/>
     <col bestFit="1" min="11" max="11" width="18.2109375"/>
@@ -4841,7 +4834,6 @@
       <c r="N4">
         <v>31.57</v>
       </c>
-      <c r="O4"/>
       <c r="P4">
         <v>54.460000000000001</v>
       </c>
@@ -5007,7 +4999,6 @@
       <c r="N7">
         <v>26.07</v>
       </c>
-      <c r="O7"/>
       <c r="P7">
         <v>99.969999999999999</v>
       </c>
@@ -5285,7 +5276,6 @@
       <c r="N12">
         <v>35.869999999999997</v>
       </c>
-      <c r="O12"/>
       <c r="P12">
         <v>59</v>
       </c>
@@ -5339,7 +5329,6 @@
       <c r="N13">
         <v>11.31</v>
       </c>
-      <c r="O13"/>
       <c r="P13">
         <v>21.420000000000002</v>
       </c>
@@ -5528,7 +5517,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="10" max="10" width="22.921875"/>
   </cols>
@@ -5688,7 +5677,6 @@
       <c r="N3">
         <v>9.5600000000000005</v>
       </c>
-      <c r="O3"/>
       <c r="P3">
         <v>62.5</v>
       </c>
@@ -5798,7 +5786,6 @@
       <c r="N5">
         <v>10.640000000000001</v>
       </c>
-      <c r="O5"/>
       <c r="P5">
         <v>85.530000000000001</v>
       </c>
@@ -6020,7 +6007,6 @@
       <c r="N9">
         <v>20.100000000000001</v>
       </c>
-      <c r="O9"/>
       <c r="P9">
         <v>283.36000000000001</v>
       </c>
@@ -6130,7 +6116,6 @@
       <c r="N11">
         <v>19.260000000000002</v>
       </c>
-      <c r="O11"/>
       <c r="P11">
         <v>61.140000000000001</v>
       </c>
@@ -6240,7 +6225,6 @@
       <c r="N13">
         <v>13.73</v>
       </c>
-      <c r="O13"/>
       <c r="P13">
         <v>88.099999999999994</v>
       </c>
@@ -6350,7 +6334,6 @@
       <c r="N15">
         <v>48.07</v>
       </c>
-      <c r="O15"/>
       <c r="P15">
         <v>150.00999999999999</v>
       </c>
@@ -6404,7 +6387,6 @@
       <c r="N16">
         <v>3.9500000000000002</v>
       </c>
-      <c r="O16"/>
       <c r="P16">
         <v>29.120000000000001</v>
       </c>
@@ -6458,7 +6440,6 @@
       <c r="N17">
         <v>10.869999999999999</v>
       </c>
-      <c r="O17"/>
       <c r="P17">
         <v>60.100000000000001</v>
       </c>
@@ -6591,7 +6572,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" customWidth="1" min="10" max="10" width="31.421875"/>
   </cols>
@@ -6751,7 +6732,6 @@
       <c r="N3">
         <v>9.5600000000000005</v>
       </c>
-      <c r="O3"/>
       <c r="P3">
         <v>62.5</v>
       </c>
@@ -6861,7 +6841,6 @@
       <c r="N5">
         <v>10.640000000000001</v>
       </c>
-      <c r="O5"/>
       <c r="P5">
         <v>85.530000000000001</v>
       </c>
@@ -7307,7 +7286,6 @@
       <c r="N13">
         <v>73.810000000000002</v>
       </c>
-      <c r="O13"/>
       <c r="P13">
         <v>59.259999999999998</v>
       </c>
@@ -7361,7 +7339,6 @@
       <c r="N14">
         <v>0.33665</v>
       </c>
-      <c r="O14"/>
       <c r="P14">
         <v>31.640000000000001</v>
       </c>
@@ -7412,8 +7389,6 @@
       <c r="M15" t="s">
         <v>23</v>
       </c>
-      <c r="N15"/>
-      <c r="O15"/>
       <c r="P15">
         <v>164.78</v>
       </c>
@@ -7434,7 +7409,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="10" max="10" width="28.3515625"/>
   </cols>
@@ -7594,7 +7569,6 @@
       <c r="N3">
         <v>114.29000000000001</v>
       </c>
-      <c r="O3"/>
       <c r="P3">
         <v>29</v>
       </c>
@@ -7872,7 +7846,6 @@
       <c r="N8">
         <v>12.449999999999999</v>
       </c>
-      <c r="O8"/>
       <c r="P8">
         <v>62.289999999999999</v>
       </c>
@@ -7982,7 +7955,6 @@
       <c r="N10">
         <v>12.109999999999999</v>
       </c>
-      <c r="O10"/>
       <c r="P10">
         <v>39.710000000000001</v>
       </c>
@@ -8778,8 +8750,6 @@
       <c r="M14" t="s">
         <v>23</v>
       </c>
-      <c r="N14"/>
-      <c r="O14"/>
       <c r="P14">
         <v>127.53</v>
       </c>
@@ -9027,7 +8997,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="10" max="10" width="22.921875"/>
   </cols>
@@ -9187,7 +9157,6 @@
       <c r="N3">
         <v>9.5600000000000005</v>
       </c>
-      <c r="O3"/>
       <c r="P3">
         <v>62.5</v>
       </c>
@@ -9297,7 +9266,6 @@
       <c r="N5">
         <v>35.469999999999999</v>
       </c>
-      <c r="O5"/>
       <c r="P5">
         <v>154.12</v>
       </c>
@@ -9351,7 +9319,6 @@
       <c r="N6">
         <v>10.640000000000001</v>
       </c>
-      <c r="O6"/>
       <c r="P6">
         <v>85.530000000000001</v>
       </c>
@@ -9853,7 +9820,6 @@
       <c r="N15">
         <v>8.1300000000000008</v>
       </c>
-      <c r="O15"/>
       <c r="P15">
         <v>15.619999999999999</v>
       </c>
@@ -10019,7 +9985,6 @@
       <c r="N18">
         <v>18.379999999999999</v>
       </c>
-      <c r="O18"/>
       <c r="P18">
         <v>130.62</v>
       </c>
@@ -10040,7 +10005,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="10" max="10" width="28.57421875"/>
     <col bestFit="1" customWidth="1" min="11" max="11" width="18.2109375"/>
@@ -10538,7 +10503,6 @@
       <c r="N9">
         <v>7.8399999999999999</v>
       </c>
-      <c r="O9"/>
       <c r="P9">
         <v>36.960000000000001</v>
       </c>
@@ -10739,7 +10703,7 @@
         <v>972539</v>
       </c>
       <c r="S2">
-        <f>N2/1000000000</f>
+        <f t="shared" ref="S2:S9" si="2">N2/1000000000</f>
         <v>33.840000000000003</v>
       </c>
     </row>
@@ -10799,7 +10763,7 @@
         <v>2953533</v>
       </c>
       <c r="S3">
-        <f>N3/1000000000</f>
+        <f t="shared" si="2"/>
         <v>38.990000000000002</v>
       </c>
     </row>
@@ -10859,7 +10823,7 @@
         <v>8302507</v>
       </c>
       <c r="S4">
-        <f>N4/1000000000</f>
+        <f t="shared" si="2"/>
         <v>19.27</v>
       </c>
     </row>
@@ -10919,7 +10883,7 @@
         <v>280886</v>
       </c>
       <c r="S5">
-        <f>N5/1000000000</f>
+        <f t="shared" si="2"/>
         <v>38.219999999999999</v>
       </c>
     </row>
@@ -10979,7 +10943,7 @@
         <v>2165877</v>
       </c>
       <c r="S6">
-        <f>N6/1000000000</f>
+        <f t="shared" si="2"/>
         <v>12.449999999999999</v>
       </c>
     </row>
@@ -11039,7 +11003,7 @@
         <v>769230</v>
       </c>
       <c r="S7">
-        <f>N7/1000000000</f>
+        <f t="shared" si="2"/>
         <v>12.99</v>
       </c>
     </row>
@@ -11099,7 +11063,7 @@
         <v>2425796</v>
       </c>
       <c r="S8">
-        <f>N8/1000000000</f>
+        <f t="shared" si="2"/>
         <v>139.71000000000001</v>
       </c>
     </row>
@@ -11159,7 +11123,7 @@
         <v>3897738</v>
       </c>
       <c r="S9">
-        <f>N9/1000000000</f>
+        <f t="shared" si="2"/>
         <v>99.189999999999998</v>
       </c>
     </row>
@@ -11219,7 +11183,7 @@
         <v>1285361</v>
       </c>
       <c r="S10">
-        <f>N10/1000000000</f>
+        <f t="shared" ref="S10:S16" si="3">N10/1000000000</f>
         <v>16.010000000000002</v>
       </c>
     </row>
@@ -11279,7 +11243,7 @@
         <v>5956238</v>
       </c>
       <c r="S11">
-        <f>N11/1000000000</f>
+        <f t="shared" si="3"/>
         <v>35.420000000000002</v>
       </c>
     </row>
@@ -11339,7 +11303,7 @@
         <v>19244004</v>
       </c>
       <c r="S12">
-        <f>N12/1000000000</f>
+        <f t="shared" si="3"/>
         <v>58.450000000000003</v>
       </c>
     </row>
@@ -11399,7 +11363,7 @@
         <v>3627350</v>
       </c>
       <c r="S13">
-        <f>N13/1000000000</f>
+        <f t="shared" si="3"/>
         <v>11.35</v>
       </c>
     </row>
@@ -11459,7 +11423,7 @@
         <v>14076265</v>
       </c>
       <c r="S14">
-        <f>N14/1000000000</f>
+        <f t="shared" si="3"/>
         <v>48.200000000000003</v>
       </c>
     </row>
@@ -11519,7 +11483,7 @@
         <v>291989</v>
       </c>
       <c r="S15">
-        <f>N15/1000000000</f>
+        <f t="shared" si="3"/>
         <v>6.6500000000000004</v>
       </c>
     </row>
@@ -11579,7 +11543,7 @@
         <v>822809</v>
       </c>
       <c r="S16">
-        <f>N16/1000000000</f>
+        <f t="shared" si="3"/>
         <v>0.88278000000000001</v>
       </c>
     </row>
@@ -12487,8 +12451,6 @@
       <c r="M16" t="s">
         <v>23</v>
       </c>
-      <c r="N16"/>
-      <c r="O16"/>
       <c r="P16">
         <v>164.78</v>
       </c>
@@ -14014,8 +13976,6 @@
       <c r="M19" t="s">
         <v>23</v>
       </c>
-      <c r="N19"/>
-      <c r="O19"/>
       <c r="P19">
         <v>164.78</v>
       </c>
@@ -14069,7 +14029,6 @@
       <c r="N20">
         <v>18.379999999999999</v>
       </c>
-      <c r="O20"/>
       <c r="P20">
         <v>130.62</v>
       </c>
@@ -14123,7 +14082,6 @@
       <c r="N21">
         <v>35.469999999999999</v>
       </c>
-      <c r="O21"/>
       <c r="P21">
         <v>154.12</v>
       </c>
@@ -14233,7 +14191,6 @@
       <c r="N23">
         <v>10.640000000000001</v>
       </c>
-      <c r="O23"/>
       <c r="P23">
         <v>85.530000000000001</v>
       </c>
@@ -14287,7 +14244,6 @@
       <c r="N24">
         <v>9.5600000000000005</v>
       </c>
-      <c r="O24"/>
       <c r="P24">
         <v>62.5</v>
       </c>
@@ -14863,7 +14819,6 @@
       <c r="N10">
         <v>24.260000000000002</v>
       </c>
-      <c r="O10"/>
       <c r="P10">
         <v>496.20999999999998</v>
       </c>
@@ -14917,7 +14872,6 @@
       <c r="N11">
         <v>40.829999999999998</v>
       </c>
-      <c r="O11"/>
       <c r="P11">
         <v>166.15000000000001</v>
       </c>
@@ -14968,8 +14922,6 @@
       <c r="M12" t="s">
         <v>23</v>
       </c>
-      <c r="N12"/>
-      <c r="O12"/>
       <c r="P12">
         <v>164.78</v>
       </c>
@@ -15023,7 +14975,6 @@
       <c r="N13">
         <v>29.739999999999998</v>
       </c>
-      <c r="O13"/>
       <c r="P13">
         <v>93.159999999999997</v>
       </c>
@@ -15077,7 +15028,6 @@
       <c r="N14">
         <v>10.640000000000001</v>
       </c>
-      <c r="O14"/>
       <c r="P14">
         <v>85.530000000000001</v>
       </c>
@@ -15131,7 +15081,6 @@
       <c r="N15">
         <v>9.5600000000000005</v>
       </c>
-      <c r="O15"/>
       <c r="P15">
         <v>62.5</v>
       </c>
@@ -15185,7 +15134,6 @@
       <c r="N16">
         <v>1.3</v>
       </c>
-      <c r="O16"/>
       <c r="P16">
         <v>28.460000000000001</v>
       </c>
@@ -15239,7 +15187,6 @@
       <c r="N17">
         <v>27.190000000000001</v>
       </c>
-      <c r="O17"/>
       <c r="P17">
         <v>13.65</v>
       </c>
@@ -15293,7 +15240,6 @@
       <c r="N18">
         <v>19.370000000000001</v>
       </c>
-      <c r="O18"/>
       <c r="P18">
         <v>66.269999999999996</v>
       </c>
@@ -15347,7 +15293,6 @@
       <c r="N19">
         <v>0.61538999999999999</v>
       </c>
-      <c r="O19"/>
       <c r="P19">
         <v>30.27</v>
       </c>
@@ -15869,7 +15814,6 @@
       <c r="N9">
         <v>114.29000000000001</v>
       </c>
-      <c r="O9"/>
       <c r="P9">
         <v>29</v>
       </c>
@@ -16144,8 +16088,6 @@
       <c r="M14" t="s">
         <v>23</v>
       </c>
-      <c r="N14"/>
-      <c r="O14"/>
       <c r="P14">
         <v>164.78</v>
       </c>
@@ -16225,7 +16167,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="10" max="10" width="28.57421875"/>
     <col bestFit="1" min="11" max="11" width="18.2109375"/>
@@ -16498,7 +16440,6 @@
       <c r="N5">
         <v>114.29000000000001</v>
       </c>
-      <c r="O5"/>
       <c r="P5">
         <v>29</v>
       </c>
@@ -17336,7 +17277,6 @@
       <c r="N20">
         <v>13.960000000000001</v>
       </c>
-      <c r="O20"/>
       <c r="P20">
         <v>7.8700000000000001</v>
       </c>
@@ -17390,7 +17330,6 @@
       <c r="N21">
         <v>13.69</v>
       </c>
-      <c r="O21"/>
       <c r="P21">
         <v>15.140000000000001</v>
       </c>
@@ -17444,7 +17383,6 @@
       <c r="N22">
         <v>12.73</v>
       </c>
-      <c r="O22"/>
       <c r="P22">
         <v>7.7000000000000002</v>
       </c>
@@ -17498,7 +17436,6 @@
       <c r="N23">
         <v>12.449999999999999</v>
       </c>
-      <c r="O23"/>
       <c r="P23">
         <v>62.289999999999999</v>
       </c>
@@ -17552,7 +17489,6 @@
       <c r="N24">
         <v>12.109999999999999</v>
       </c>
-      <c r="O24"/>
       <c r="P24">
         <v>39.710000000000001</v>
       </c>
@@ -17606,7 +17542,6 @@
       <c r="N25">
         <v>10.640000000000001</v>
       </c>
-      <c r="O25"/>
       <c r="P25">
         <v>85.530000000000001</v>
       </c>
@@ -17716,7 +17651,6 @@
       <c r="N27">
         <v>7.7000000000000002</v>
       </c>
-      <c r="O27"/>
       <c r="P27">
         <v>33.939999999999998</v>
       </c>
@@ -17826,7 +17760,6 @@
       <c r="N29">
         <v>2.98</v>
       </c>
-      <c r="O29"/>
       <c r="P29">
         <v>10.5</v>
       </c>
@@ -17880,7 +17813,6 @@
       <c r="N30">
         <v>2.1699999999999999</v>
       </c>
-      <c r="O30"/>
       <c r="P30">
         <v>6.4400000000000004</v>
       </c>
@@ -17990,7 +17922,6 @@
       <c r="N32">
         <v>0.28799999999999998</v>
       </c>
-      <c r="O32"/>
       <c r="P32">
         <v>0.58999999999999997</v>
       </c>
@@ -18020,7 +17951,7 @@
   <cols>
     <col bestFit="1" min="8" max="8" width="12.8515625"/>
     <col bestFit="1" min="10" max="10" width="32.50390625"/>
-    <col bestFit="1" min="11" max="11" width="18.2109375"/>
+    <col customWidth="1" min="11" max="11" width="21.28125"/>
     <col bestFit="1" min="12" max="12" width="27.28125"/>
   </cols>
   <sheetData>
@@ -18123,7 +18054,6 @@
       <c r="N2">
         <v>26.850000000000001</v>
       </c>
-      <c r="O2"/>
       <c r="P2">
         <v>83.849999999999994</v>
       </c>
@@ -18569,7 +18499,6 @@
       <c r="N10">
         <v>13.35</v>
       </c>
-      <c r="O10"/>
       <c r="P10">
         <v>19.870000000000001</v>
       </c>
